--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260908.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260908.xlsx
@@ -1019,17 +1019,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>367,497,947</t>
+          <t>7,118,766</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>7,118,766</t>
+          <t>367,497,947</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>永豐金</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>44,952,407</t>
+          <t>301,003,890</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>永豐金</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>301,003,890</t>
+          <t>44,952,407</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>257,654,021</t>
+          <t>213,603,636</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>213,603,636</t>
+          <t>257,654,021</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
